--- a/MesureGraphiteSensor.xlsx
+++ b/MesureGraphiteSensor.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\Projet_capteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B9A2360-E1AD-413A-8D77-6CFEE7D3DB54}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C582B5-150C-4321-AA93-F1ABEB76569D}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9048" activeTab="1" xr2:uid="{26616443-A70B-4F30-8590-3C8F2284DA29}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9048" firstSheet="1" activeTab="1" xr2:uid="{26616443-A70B-4F30-8590-3C8F2284DA29}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
     <sheet name="Mise en tension" sheetId="2" r:id="rId2"/>
-    <sheet name="Mise en Compression" sheetId="3" r:id="rId3"/>
+    <sheet name="Mise en compression" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -92,7 +92,7 @@
     <author>Y</author>
   </authors>
   <commentList>
-    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{B23A6775-1F38-4D1C-A169-FCC8B1D3E988}">
+    <comment ref="E9" authorId="0" shapeId="0" xr:uid="{B23A6775-1F38-4D1C-A169-FCC8B1D3E988}">
       <text>
         <r>
           <rPr>
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="22">
   <si>
     <t>Graphite Sensor</t>
   </si>
@@ -159,12 +159,42 @@
   <si>
     <t>Déformation</t>
   </si>
+  <si>
+    <t>pot 128</t>
+  </si>
+  <si>
+    <t>Crayon HB</t>
+  </si>
+  <si>
+    <t>pot 1</t>
+  </si>
+  <si>
+    <t>Crayon 2B</t>
+  </si>
+  <si>
+    <t>pot …</t>
+  </si>
+  <si>
+    <t>COMPRESSION</t>
+  </si>
+  <si>
+    <t>TENSION</t>
+  </si>
+  <si>
+    <t>pot 43</t>
+  </si>
+  <si>
+    <t>ΔR/R0</t>
+  </si>
+  <si>
+    <t>pot 4</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,16 +215,40 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -202,12 +256,110 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -223,6 +375,3758 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Mise en tension'!$H$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ΔR/R0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Mise en tension'!$D$17:$D$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.6666666666666671E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.7142857142857143E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.4444444444444444E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Mise en tension'!$H$17:$H$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.2292530259875397E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.27481127276802436</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.32813464277039384</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.47082470316864478</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.55429295945687818</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.54823416602951858</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1EFE-4F94-A9C5-8D6D8F80D1B5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1263235791"/>
+        <c:axId val="944977199"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1263235791"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="944977199"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="944977199"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1263235791"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Mise en tension'!$H$27</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ΔR/R0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Mise en tension'!$D$28:$D$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.6666666666666671E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.7142857142857143E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.4444444444444444E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Mise en tension'!$H$28:$H$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.63856469630663215</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.30559882631919938</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.25792532951334979</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.13561473893719692</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.10676887640305498</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.9344093409720859E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2ED9-4A90-B16E-20D4252817E2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1258779983"/>
+        <c:axId val="1388343279"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1258779983"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1388343279"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1388343279"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1258779983"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Mise en compression'!$H$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ΔR/R0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Mise en compression'!$D$17:$D$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.4999999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.6E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.3333333333333332E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.4285714285714284E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.7499999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.2222222222222227E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Mise en compression'!$H$17:$H$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.383780565665713</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.42624306851264204</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.52467899707992482</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.58633949243030836</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-0.61339280289543296</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-0.44903876473657039</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2123-4E11-ADC7-0AB70703AD67}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1257198911"/>
+        <c:axId val="944970543"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1257198911"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="944970543"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="944970543"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1257198911"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Mise en compression'!$H$27</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ΔR/R0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Mise en compression'!$D$28:$D$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.4999999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.6E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.3333333333333332E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.4285714285714284E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.7499999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.2222222222222227E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Mise en compression'!$H$28:$H$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.59354869101315466</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.57558340403656116</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.54783755009603174</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.49943657165211042</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-0.45015800059293426</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-0.42458707096112186</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-73B4-498D-8AAF-68F4B67558BA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1258761183"/>
+        <c:axId val="1388341199"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1258761183"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1388341199"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1388341199"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1258761183"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>548640</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>118110</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>365760</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>118110</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Graphique 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9FDDE150-DF85-4D0C-8F25-4CE38BDF8523}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>64770</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>426720</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>64770</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Graphique 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09941FD7-04AA-474A-9CAB-B5451486403A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>125730</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>121920</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>125730</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Graphique 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDD96944-CF81-4243-8F53-4A6482B46067}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>510540</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>327660</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Graphique 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67793210-6FCE-406B-9BCB-4212D1A6BB26}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -574,8 +4478,8 @@
         <v>0.01</v>
       </c>
       <c r="C7">
-        <f>'Mise en tension'!$B$1/(2*B7)</f>
-        <v>9.5</v>
+        <f>'Mise en tension'!$B$2/(2*B7)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -583,8 +4487,8 @@
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="C8">
-        <f>'Mise en tension'!$B$1/(2*B8)</f>
-        <v>7.6</v>
+        <f>'Mise en tension'!$B$2/(2*B8)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -592,8 +4496,8 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="C9">
-        <f>'Mise en tension'!$B$1/(2*B9)</f>
-        <v>6.3333333333333339</v>
+        <f>'Mise en tension'!$B$2/(2*B9)</f>
+        <v>6.666666666666667</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -601,8 +4505,8 @@
         <v>1.7500000000000002E-2</v>
       </c>
       <c r="C10">
-        <f>'Mise en tension'!$B$1/(2*B10)</f>
-        <v>5.4285714285714279</v>
+        <f>'Mise en tension'!$B$2/(2*B10)</f>
+        <v>5.7142857142857144</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -613,8 +4517,8 @@
         <v>0.02</v>
       </c>
       <c r="C11">
-        <f>'Mise en tension'!$B$1/(2*B11)</f>
-        <v>4.75</v>
+        <f>'Mise en tension'!$B$2/(2*B11)</f>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>2.52</v>
@@ -628,8 +4532,8 @@
         <v>2.2499999999999999E-2</v>
       </c>
       <c r="C12">
-        <f>'Mise en tension'!$B$1/(2*B12)</f>
-        <v>4.2222222222222223</v>
+        <f>'Mise en tension'!$B$2/(2*B12)</f>
+        <v>4.4444444444444446</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -640,8 +4544,8 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="C13">
-        <f>'Mise en tension'!$B$1/(2*B13)</f>
-        <v>3.8</v>
+        <f>'Mise en tension'!$B$2/(2*B13)</f>
+        <v>4</v>
       </c>
       <c r="D13">
         <v>2.35</v>
@@ -658,8 +4562,8 @@
         <v>0.03</v>
       </c>
       <c r="C14">
-        <f>'Mise en tension'!$B$1/(2*B14)</f>
-        <v>3.166666666666667</v>
+        <f>'Mise en tension'!$B$2/(2*B14)</f>
+        <v>3.3333333333333335</v>
       </c>
       <c r="D14">
         <v>2.31</v>
@@ -676,8 +4580,8 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="C15">
-        <f>'Mise en tension'!$B$1/(2*B15)</f>
-        <v>2.714285714285714</v>
+        <f>'Mise en tension'!$B$2/(2*B15)</f>
+        <v>2.8571428571428572</v>
       </c>
       <c r="D15">
         <v>1.96</v>
@@ -691,8 +4595,8 @@
         <v>0.04</v>
       </c>
       <c r="C16">
-        <f>'Mise en tension'!$B$1/(2*B16)</f>
-        <v>2.375</v>
+        <f>'Mise en tension'!$B$2/(2*B16)</f>
+        <v>2.5</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -700,8 +4604,8 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="C17">
-        <f>'Mise en tension'!$B$1/(2*B17)</f>
-        <v>2.1111111111111112</v>
+        <f>'Mise en tension'!$B$2/(2*B17)</f>
+        <v>2.2222222222222223</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -712,8 +4616,8 @@
         <v>1</v>
       </c>
       <c r="C21">
-        <f>'Mise en tension'!$B$1/(2*B21)</f>
-        <v>9.5000000000000001E-2</v>
+        <f>'Mise en tension'!$B$2/(2*B21)</f>
+        <v>0.1</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -724,8 +4628,8 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="C22">
-        <f>'Mise en tension'!$B$1/(2*B22)</f>
-        <v>2.1111111111111112</v>
+        <f>'Mise en tension'!$B$2/(2*B22)</f>
+        <v>2.2222222222222223</v>
       </c>
       <c r="D22">
         <v>2.52</v>
@@ -742,8 +4646,8 @@
         <v>0.04</v>
       </c>
       <c r="C23">
-        <f>'Mise en tension'!$B$1/(2*B23)</f>
-        <v>2.375</v>
+        <f>'Mise en tension'!$B$2/(2*B23)</f>
+        <v>2.5</v>
       </c>
       <c r="D23">
         <v>2.35</v>
@@ -760,8 +4664,8 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="C24">
-        <f>'Mise en tension'!$B$1/(2*B24)</f>
-        <v>2.714285714285714</v>
+        <f>'Mise en tension'!$B$2/(2*B24)</f>
+        <v>2.8571428571428572</v>
       </c>
       <c r="D24">
         <v>2.31</v>
@@ -778,8 +4682,8 @@
         <v>0.03</v>
       </c>
       <c r="C25">
-        <f>'Mise en tension'!$B$1/(2*B25)</f>
-        <v>3.166666666666667</v>
+        <f>'Mise en tension'!$B$2/(2*B25)</f>
+        <v>3.3333333333333335</v>
       </c>
       <c r="D25">
         <v>1.96</v>
@@ -796,8 +4700,8 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="C26">
-        <f>'Mise en tension'!$B$1/(2*B26)</f>
-        <v>3.8</v>
+        <f>'Mise en tension'!$B$2/(2*B26)</f>
+        <v>4</v>
       </c>
       <c r="D26">
         <v>1.99</v>
@@ -814,8 +4718,8 @@
         <v>0.02</v>
       </c>
       <c r="C27">
-        <f>'Mise en tension'!$B$1/(2*B27)</f>
-        <v>4.75</v>
+        <f>'Mise en tension'!$B$2/(2*B27)</f>
+        <v>5</v>
       </c>
       <c r="D27">
         <v>1.95</v>
@@ -833,355 +4737,1516 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9AF43EA-3DC9-4855-BEED-2A1578264041}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:H45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.88671875" customWidth="1"/>
+    <col min="2" max="2" width="7.77734375" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.109375" customWidth="1"/>
+    <col min="6" max="6" width="18.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2">
+        <v>0.2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>4.99</v>
+      </c>
+      <c r="F6">
+        <v>80146904</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <f>1/$B7</f>
+        <v>0.1</v>
+      </c>
+      <c r="D7">
+        <f>$B$2/(2*$B7)</f>
+        <v>0.01</v>
+      </c>
+      <c r="E7">
+        <v>2.52</v>
+      </c>
+      <c r="F7">
+        <v>158692912</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <v>12.5</v>
+      </c>
+      <c r="C8">
+        <f t="shared" ref="C8:C12" si="0">1/$B8</f>
+        <v>0.08</v>
+      </c>
+      <c r="D8">
+        <f t="shared" ref="D8:D12" si="1">$B$2/(2*$B8)</f>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="E8">
+        <v>2.35</v>
+      </c>
+      <c r="F8">
+        <v>170603136</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>15</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="1"/>
+        <v>6.6666666666666671E-3</v>
+      </c>
+      <c r="E9">
+        <v>2.31</v>
+      </c>
+      <c r="F9">
+        <v>173129536</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>4</v>
+      </c>
+      <c r="B10">
+        <v>17.5</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>5.7142857142857141E-2</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="1"/>
+        <v>5.7142857142857143E-3</v>
+      </c>
+      <c r="E10">
+        <v>1.96</v>
+      </c>
+      <c r="F10">
+        <v>203726560</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11">
+        <v>20</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="1"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E11">
+        <v>1.99</v>
+      </c>
+      <c r="F11">
+        <v>201222432</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>6</v>
+      </c>
+      <c r="B12">
+        <v>22.5</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>4.4444444444444446E-2</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="1"/>
+        <v>4.4444444444444444E-3</v>
+      </c>
+      <c r="E12">
+        <v>1.95</v>
+      </c>
+      <c r="F12">
+        <v>205259168</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>5</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>3.89</v>
+      </c>
+      <c r="F17">
+        <v>39012388</v>
+      </c>
+      <c r="H17">
+        <f>(F17-$F$17)/$F$17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18">
+        <v>10</v>
+      </c>
+      <c r="C18">
+        <f>1/$B18</f>
+        <v>0.1</v>
+      </c>
+      <c r="D18">
+        <f>$B$2/(2*$B18)</f>
+        <v>0.01</v>
+      </c>
+      <c r="E18">
+        <v>3.56</v>
+      </c>
+      <c r="F18">
+        <v>42612940</v>
+      </c>
+      <c r="H18">
+        <f t="shared" ref="H18:H23" si="2">(F18-$F$17)/$F$17</f>
+        <v>9.2292530259875397E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19">
+        <v>12.5</v>
+      </c>
+      <c r="C19">
+        <f t="shared" ref="C19:C23" si="3">1/$B19</f>
+        <v>0.08</v>
+      </c>
+      <c r="D19">
+        <f t="shared" ref="D19:D23" si="4">$B$2/(2*$B19)</f>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="E19">
+        <v>3.05</v>
+      </c>
+      <c r="F19">
+        <v>49733432</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="2"/>
+        <v>0.27481127276802436</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>15</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="3"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="4"/>
+        <v>6.6666666666666671E-3</v>
+      </c>
+      <c r="E20">
+        <v>2.93</v>
+      </c>
+      <c r="F20">
+        <v>51813704</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="2"/>
+        <v>0.32813464277039384</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>4</v>
+      </c>
+      <c r="B21">
+        <v>17.5</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="3"/>
+        <v>5.7142857142857141E-2</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="4"/>
+        <v>5.7142857142857143E-3</v>
+      </c>
+      <c r="E21">
+        <v>2.64</v>
+      </c>
+      <c r="F21">
+        <v>57380384</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="2"/>
+        <v>0.47082470316864478</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>5</v>
+      </c>
+      <c r="B22">
+        <v>20</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="3"/>
+        <v>0.05</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="4"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E22">
+        <v>2.5</v>
+      </c>
+      <c r="F22">
+        <v>60636680</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="2"/>
+        <v>0.55429295945687818</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>6</v>
+      </c>
+      <c r="B23">
+        <v>22.5</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="3"/>
+        <v>4.4444444444444446E-2</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="4"/>
+        <v>4.4444444444444444E-3</v>
+      </c>
+      <c r="E23">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="F23">
+        <v>60400312</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="2"/>
+        <v>0.54823416602951858</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="7"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" s="9"/>
+      <c r="H27" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="8">
+        <v>0</v>
+      </c>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9">
+        <v>0</v>
+      </c>
+      <c r="D28" s="9">
+        <v>0</v>
+      </c>
+      <c r="E28" s="9">
+        <v>3.21</v>
+      </c>
+      <c r="F28" s="9">
+        <v>16470577</v>
+      </c>
+      <c r="G28" s="9"/>
+      <c r="H28" s="11">
+        <f>(F28-$F$28)/$F$28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="8">
+        <v>1</v>
+      </c>
+      <c r="B29" s="9">
+        <v>10</v>
+      </c>
+      <c r="C29" s="9">
+        <f>1/$B29</f>
+        <v>0.1</v>
+      </c>
+      <c r="D29" s="9">
+        <f>$B$2/(2*$B29)</f>
+        <v>0.01</v>
+      </c>
+      <c r="E29" s="9">
+        <v>1.96</v>
+      </c>
+      <c r="F29" s="9">
+        <v>26988106</v>
+      </c>
+      <c r="G29" s="9"/>
+      <c r="H29" s="11">
+        <f>(F29-$F$28)/$F$28</f>
+        <v>0.63856469630663215</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="8">
+        <v>2</v>
+      </c>
+      <c r="B30" s="9">
+        <v>12.5</v>
+      </c>
+      <c r="C30" s="9">
+        <f t="shared" ref="C30:C34" si="5">1/$B30</f>
+        <v>0.08</v>
+      </c>
+      <c r="D30" s="9">
+        <f t="shared" ref="D30:D34" si="6">$B$2/(2*$B30)</f>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="E30" s="9">
+        <v>2.46</v>
+      </c>
+      <c r="F30" s="9">
+        <v>21503966</v>
+      </c>
+      <c r="G30" s="9"/>
+      <c r="H30" s="11">
+        <f>(F30-$F$28)/$F$28</f>
+        <v>0.30559882631919938</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="8">
+        <v>3</v>
+      </c>
+      <c r="B31" s="9">
+        <v>15</v>
+      </c>
+      <c r="C31" s="9">
+        <f t="shared" si="5"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="D31" s="9">
+        <f t="shared" si="6"/>
+        <v>6.6666666666666671E-3</v>
+      </c>
+      <c r="E31" s="9">
+        <v>2.56</v>
+      </c>
+      <c r="F31" s="9">
+        <v>20718756</v>
+      </c>
+      <c r="G31" s="9"/>
+      <c r="H31" s="11">
+        <f>(F31-$F$28)/$F$28</f>
+        <v>0.25792532951334979</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="8">
+        <v>4</v>
+      </c>
+      <c r="B32" s="9">
+        <v>17.5</v>
+      </c>
+      <c r="C32" s="9">
+        <f t="shared" si="5"/>
+        <v>5.7142857142857141E-2</v>
+      </c>
+      <c r="D32" s="9">
+        <f t="shared" si="6"/>
+        <v>5.7142857142857143E-3</v>
+      </c>
+      <c r="E32" s="9">
+        <v>2.83</v>
+      </c>
+      <c r="F32" s="9">
+        <v>18704230</v>
+      </c>
+      <c r="G32" s="9"/>
+      <c r="H32" s="11">
+        <f>(F32-$F$28)/$F$28</f>
+        <v>0.13561473893719692</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="8">
+        <v>5</v>
+      </c>
+      <c r="B33" s="9">
+        <v>20</v>
+      </c>
+      <c r="C33" s="9">
+        <f t="shared" si="5"/>
+        <v>0.05</v>
+      </c>
+      <c r="D33" s="9">
+        <f t="shared" si="6"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E33" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="F33" s="9">
+        <v>18229122</v>
+      </c>
+      <c r="G33" s="9"/>
+      <c r="H33" s="11">
+        <f>(F33-$F$28)/$F$28</f>
+        <v>0.10676887640305498</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="12">
+        <v>6</v>
+      </c>
+      <c r="B34" s="13">
+        <v>22.5</v>
+      </c>
+      <c r="C34" s="13">
+        <f t="shared" si="5"/>
+        <v>4.4444444444444446E-2</v>
+      </c>
+      <c r="D34" s="13">
+        <f t="shared" si="6"/>
+        <v>4.4444444444444444E-3</v>
+      </c>
+      <c r="E34" s="13">
+        <v>2.98</v>
+      </c>
+      <c r="F34" s="13">
+        <v>17777420</v>
+      </c>
+      <c r="G34" s="13"/>
+      <c r="H34" s="14">
+        <f>(F34-$F$28)/$F$28</f>
+        <v>7.9344093409720859E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>1</v>
+      </c>
+      <c r="B40">
+        <v>10</v>
+      </c>
+      <c r="C40">
+        <f>1/$B40</f>
+        <v>0.1</v>
+      </c>
+      <c r="D40">
+        <f>$B$2/(2*$B40)</f>
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>2</v>
+      </c>
+      <c r="B41">
+        <v>12.5</v>
+      </c>
+      <c r="C41">
+        <f t="shared" ref="C41:C45" si="7">1/$B41</f>
+        <v>0.08</v>
+      </c>
+      <c r="D41">
+        <f t="shared" ref="D41:D45" si="8">$B$2/(2*$B41)</f>
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>3</v>
+      </c>
+      <c r="B42">
+        <v>15</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="7"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="D42">
+        <f t="shared" si="8"/>
+        <v>6.6666666666666671E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>4</v>
+      </c>
+      <c r="B43">
+        <v>17.5</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="7"/>
+        <v>5.7142857142857141E-2</v>
+      </c>
+      <c r="D43">
+        <f t="shared" si="8"/>
+        <v>5.7142857142857143E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>5</v>
+      </c>
+      <c r="B44">
+        <v>20</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="7"/>
+        <v>0.05</v>
+      </c>
+      <c r="D44">
+        <f t="shared" si="8"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>6</v>
+      </c>
+      <c r="B45">
+        <v>22.5</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="7"/>
+        <v>4.4444444444444446E-2</v>
+      </c>
+      <c r="D45">
+        <f t="shared" si="8"/>
+        <v>4.4444444444444444E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07B17566-2D0F-4854-8779-E2AD22D057CD}">
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" customWidth="1"/>
     <col min="3" max="3" width="15.77734375" customWidth="1"/>
     <col min="4" max="4" width="18.109375" customWidth="1"/>
     <col min="6" max="6" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B1">
+      <c r="B2">
         <v>0.19</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D5" t="s">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E5" t="s">
         <v>1</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>0</v>
       </c>
-      <c r="C5">
+      <c r="C6">
         <v>0</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>0</v>
       </c>
-      <c r="E5">
-        <v>4.99</v>
-      </c>
-      <c r="F5">
-        <v>80146904</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>1</v>
       </c>
-      <c r="B6">
+      <c r="B7">
         <v>10</v>
       </c>
-      <c r="C6">
-        <f>1/B6</f>
+      <c r="C7">
+        <f>1/$B7</f>
         <v>0.1</v>
       </c>
-      <c r="D6">
-        <f>$B$1/(2*B6)</f>
+      <c r="D7">
+        <f>$B$2/(2*$B7)</f>
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="E6">
-        <v>2.52</v>
-      </c>
-      <c r="F6">
-        <v>158692912</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>2</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>12.5</v>
       </c>
-      <c r="C7">
-        <f t="shared" ref="C7:C11" si="0">1/B7</f>
+      <c r="C8">
+        <f t="shared" ref="C8:C12" si="0">1/$B8</f>
         <v>0.08</v>
       </c>
-      <c r="D7">
-        <f t="shared" ref="D7:D11" si="1">$B$1/(2*B7)</f>
+      <c r="D8">
+        <f t="shared" ref="D8:D12" si="1">$B$2/(2*$B8)</f>
         <v>7.6E-3</v>
       </c>
-      <c r="E7">
-        <v>2.35</v>
-      </c>
-      <c r="F7">
-        <v>170603136</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>3</v>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>15</v>
       </c>
-      <c r="C8">
+      <c r="C9">
         <f t="shared" si="0"/>
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="D8">
+      <c r="D9">
         <f t="shared" si="1"/>
         <v>6.3333333333333332E-3</v>
       </c>
-      <c r="E8">
-        <v>2.31</v>
-      </c>
-      <c r="F8">
-        <v>173129536</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>4</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>17.5</v>
       </c>
-      <c r="C9">
+      <c r="C10">
         <f t="shared" si="0"/>
         <v>5.7142857142857141E-2</v>
       </c>
-      <c r="D9">
+      <c r="D10">
         <f t="shared" si="1"/>
         <v>5.4285714285714284E-3</v>
       </c>
-      <c r="E9">
-        <v>1.96</v>
-      </c>
-      <c r="F9">
-        <v>203726560</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>5</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>20</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <f t="shared" si="0"/>
         <v>0.05</v>
       </c>
-      <c r="D10">
+      <c r="D11">
         <f t="shared" si="1"/>
         <v>4.7499999999999999E-3</v>
       </c>
-      <c r="E10">
-        <v>1.99</v>
-      </c>
-      <c r="F10">
-        <v>201222432</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11">
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12">
         <v>6</v>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>22.5</v>
       </c>
-      <c r="C11">
+      <c r="C12">
         <f t="shared" si="0"/>
         <v>4.4444444444444446E-2</v>
       </c>
-      <c r="D11">
+      <c r="D12">
         <f t="shared" si="1"/>
         <v>4.2222222222222227E-3</v>
       </c>
-      <c r="E11">
-        <v>1.95</v>
-      </c>
-      <c r="F11">
-        <v>205259168</v>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>5</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0.21</v>
+      </c>
+      <c r="F17">
+        <v>29461570</v>
+      </c>
+      <c r="H17">
+        <f>(F17-$F$17)/$F$17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18">
+        <v>10</v>
+      </c>
+      <c r="C18">
+        <f>1/$B18</f>
+        <v>0.1</v>
+      </c>
+      <c r="D18">
+        <f>$B$2/(2*$B18)</f>
+        <v>9.4999999999999998E-3</v>
+      </c>
+      <c r="E18">
+        <v>0.33</v>
+      </c>
+      <c r="F18">
+        <v>18154792</v>
+      </c>
+      <c r="H18">
+        <f t="shared" ref="H18:H23" si="2">(F18-$F$17)/$F$17</f>
+        <v>-0.383780565665713</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19">
+        <v>12.5</v>
+      </c>
+      <c r="C19">
+        <f t="shared" ref="C19:C23" si="3">1/$B19</f>
+        <v>0.08</v>
+      </c>
+      <c r="D19">
+        <f t="shared" ref="D19:D23" si="4">$B$2/(2*$B19)</f>
+        <v>7.6E-3</v>
+      </c>
+      <c r="E19">
+        <v>0.36</v>
+      </c>
+      <c r="F19">
+        <v>16903780</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="2"/>
+        <v>-0.42624306851264204</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>15</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="3"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="4"/>
+        <v>6.3333333333333332E-3</v>
+      </c>
+      <c r="E20">
+        <v>0.43</v>
+      </c>
+      <c r="F20">
+        <v>14003703</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="2"/>
+        <v>-0.52467899707992482</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>4</v>
+      </c>
+      <c r="B21">
+        <v>17.5</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="3"/>
+        <v>5.7142857142857141E-2</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="4"/>
+        <v>5.4285714285714284E-3</v>
+      </c>
+      <c r="E21">
+        <v>0.49</v>
+      </c>
+      <c r="F21">
+        <v>12187088</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="2"/>
+        <v>-0.58633949243030836</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>5</v>
+      </c>
+      <c r="B22">
+        <v>20</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="3"/>
+        <v>0.05</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="4"/>
+        <v>4.7499999999999999E-3</v>
+      </c>
+      <c r="E22">
+        <v>0.53</v>
+      </c>
+      <c r="F22">
+        <v>11390055</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="2"/>
+        <v>-0.61339280289543296</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>6</v>
+      </c>
+      <c r="B23">
+        <v>22.5</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="3"/>
+        <v>4.4444444444444446E-2</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="4"/>
+        <v>4.2222222222222227E-3</v>
+      </c>
+      <c r="E23">
+        <v>0.37</v>
+      </c>
+      <c r="F23">
+        <v>16232183</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="2"/>
+        <v>-0.44903876473657039</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" t="s">
+        <v>5</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0.85</v>
+      </c>
+      <c r="F28">
+        <v>62495968</v>
+      </c>
+      <c r="H28">
+        <f>(F28-$F$28)/$F$28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>1</v>
+      </c>
+      <c r="B29">
+        <v>10</v>
+      </c>
+      <c r="C29">
+        <f>1/$B29</f>
+        <v>0.1</v>
+      </c>
+      <c r="D29">
+        <f>$B$2/(2*$B29)</f>
+        <v>9.4999999999999998E-3</v>
+      </c>
+      <c r="E29">
+        <v>2.09</v>
+      </c>
+      <c r="F29">
+        <v>25401568</v>
+      </c>
+      <c r="H29">
+        <f t="shared" ref="H29:H34" si="5">(F29-$F$28)/$F$28</f>
+        <v>-0.59354869101315466</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>2</v>
+      </c>
+      <c r="B30">
+        <v>12.5</v>
+      </c>
+      <c r="C30">
+        <f t="shared" ref="C30:C34" si="6">1/$B30</f>
+        <v>0.08</v>
+      </c>
+      <c r="D30">
+        <f t="shared" ref="D30:D34" si="7">$B$2/(2*$B30)</f>
+        <v>7.6E-3</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+      <c r="F30">
+        <v>26524326</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="5"/>
+        <v>-0.57558340403656116</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>3</v>
+      </c>
+      <c r="B31">
+        <v>15</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="6"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="7"/>
+        <v>6.3333333333333332E-3</v>
+      </c>
+      <c r="E31">
+        <v>1.88</v>
+      </c>
+      <c r="F31">
+        <v>28258330</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="5"/>
+        <v>-0.54783755009603174</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
+        <v>17.5</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="6"/>
+        <v>5.7142857142857141E-2</v>
+      </c>
+      <c r="D32">
+        <f t="shared" si="7"/>
+        <v>5.4285714285714284E-3</v>
+      </c>
+      <c r="E32">
+        <v>1.7</v>
+      </c>
+      <c r="F32">
+        <v>31283196</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="5"/>
+        <v>-0.49943657165211042</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>5</v>
+      </c>
+      <c r="B33">
+        <v>20</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="6"/>
+        <v>0.05</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="7"/>
+        <v>4.7499999999999999E-3</v>
+      </c>
+      <c r="E33">
+        <v>1.54</v>
+      </c>
+      <c r="F33">
+        <v>34362908</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="5"/>
+        <v>-0.45015800059293426</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>6</v>
+      </c>
+      <c r="B34">
+        <v>22.5</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="6"/>
+        <v>4.4444444444444446E-2</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="7"/>
+        <v>4.2222222222222227E-3</v>
+      </c>
+      <c r="E34">
+        <v>1.48</v>
+      </c>
+      <c r="F34">
+        <v>35960988</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="5"/>
+        <v>-0.42458707096112186</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>1</v>
+      </c>
+      <c r="B40">
+        <v>10</v>
+      </c>
+      <c r="C40">
+        <f>1/$B40</f>
+        <v>0.1</v>
+      </c>
+      <c r="D40">
+        <f>$B$2/(2*$B40)</f>
+        <v>9.4999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>2</v>
+      </c>
+      <c r="B41">
+        <v>12.5</v>
+      </c>
+      <c r="C41">
+        <f t="shared" ref="C41:C45" si="8">1/$B41</f>
+        <v>0.08</v>
+      </c>
+      <c r="D41">
+        <f t="shared" ref="D41:D45" si="9">$B$2/(2*$B41)</f>
+        <v>7.6E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>3</v>
+      </c>
+      <c r="B42">
+        <v>15</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="8"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="D42">
+        <f t="shared" si="9"/>
+        <v>6.3333333333333332E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>4</v>
+      </c>
+      <c r="B43">
+        <v>17.5</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="8"/>
+        <v>5.7142857142857141E-2</v>
+      </c>
+      <c r="D43">
+        <f t="shared" si="9"/>
+        <v>5.4285714285714284E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>5</v>
+      </c>
+      <c r="B44">
+        <v>20</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="8"/>
+        <v>0.05</v>
+      </c>
+      <c r="D44">
+        <f t="shared" si="9"/>
+        <v>4.7499999999999999E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>6</v>
+      </c>
+      <c r="B45">
+        <v>22.5</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="8"/>
+        <v>4.4444444444444446E-2</v>
+      </c>
+      <c r="D45">
+        <f t="shared" si="9"/>
+        <v>4.2222222222222227E-3</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70BAF0D7-39AE-4084-9990-73C2329F5B1A}">
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1">
-        <v>0.19</v>
-      </c>
-      <c r="C1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>10</v>
-      </c>
-      <c r="C6">
-        <f>1/B6</f>
-        <v>0.1</v>
-      </c>
-      <c r="D6">
-        <f>$B$1/(2*B6)</f>
-        <v>9.4999999999999998E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7">
-        <v>12.5</v>
-      </c>
-      <c r="C7">
-        <f t="shared" ref="C7:C11" si="0">1/B7</f>
-        <v>0.08</v>
-      </c>
-      <c r="D7">
-        <f t="shared" ref="D7:D11" si="1">$B$1/(2*B7)</f>
-        <v>7.6E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>3</v>
-      </c>
-      <c r="B8">
-        <v>15</v>
-      </c>
-      <c r="C8">
-        <f t="shared" si="0"/>
-        <v>6.6666666666666666E-2</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="1"/>
-        <v>6.3333333333333332E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>4</v>
-      </c>
-      <c r="B9">
-        <v>17.5</v>
-      </c>
-      <c r="C9">
-        <f t="shared" si="0"/>
-        <v>5.7142857142857141E-2</v>
-      </c>
-      <c r="D9">
-        <f t="shared" si="1"/>
-        <v>5.4285714285714284E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>5</v>
-      </c>
-      <c r="B10">
-        <v>20</v>
-      </c>
-      <c r="C10">
-        <f t="shared" si="0"/>
-        <v>0.05</v>
-      </c>
-      <c r="D10">
-        <f t="shared" si="1"/>
-        <v>4.7499999999999999E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>6</v>
-      </c>
-      <c r="B11">
-        <v>22.5</v>
-      </c>
-      <c r="C11">
-        <f t="shared" si="0"/>
-        <v>4.4444444444444446E-2</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="1"/>
-        <v>4.2222222222222227E-3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/MesureGraphiteSensor.xlsx
+++ b/MesureGraphiteSensor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\Projet_capteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C582B5-150C-4321-AA93-F1ABEB76569D}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD14D163-0D69-495F-ADBC-348FFBE347FF}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9048" firstSheet="1" activeTab="1" xr2:uid="{26616443-A70B-4F30-8590-3C8F2284DA29}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9048" firstSheet="1" activeTab="2" xr2:uid="{26616443-A70B-4F30-8590-3C8F2284DA29}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="26">
   <si>
     <t>Graphite Sensor</t>
   </si>
@@ -169,9 +169,6 @@
     <t>pot 1</t>
   </si>
   <si>
-    <t>Crayon 2B</t>
-  </si>
-  <si>
     <t>pot …</t>
   </si>
   <si>
@@ -188,6 +185,21 @@
   </si>
   <si>
     <t>pot 4</t>
+  </si>
+  <si>
+    <t>Crayon B</t>
+  </si>
+  <si>
+    <t>Crayon 4B</t>
+  </si>
+  <si>
+    <t>pot 5</t>
+  </si>
+  <si>
+    <t>pot 3</t>
+  </si>
+  <si>
+    <t>*</t>
   </si>
 </sst>
 </file>
@@ -343,12 +355,6 @@
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -360,6 +366,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1112,6 +1124,346 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
+              <c:f>'Mise en tension'!$H$49</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ΔR/R0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Mise en tension'!$D$50:$D$56</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.6666666666666671E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.7142857142857143E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.4444444444444444E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Mise en tension'!$H$50:$H$56</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.7143622911899143E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.041951805366454E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.3778025057053817E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.7217501072546038E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.1756384504392979E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.3442132737860361E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6ACD-4676-9CE5-78227EAB0CC4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="472024511"/>
+        <c:axId val="585943567"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="472024511"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="585943567"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="585943567"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="472024511"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
               <c:f>'Mise en compression'!$H$16</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
@@ -1397,7 +1749,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
@@ -1696,6 +2048,346 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="1258761183"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Mise en compression'!$H$49</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ΔR/R0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Mise en compression'!$D$50:$D$56</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.4999999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.6E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.3333333333333332E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.4285714285714284E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.7499999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.2222222222222227E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Mise en compression'!$H$50:$H$56</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.1073767184930019</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-7.4235786371396967E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-6.7944589784440956E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-1.436822183770024E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-6.1567514681297446E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.0027954965052128E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-174E-47DB-AF52-24A4DC2F1BCB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="581013855"/>
+        <c:axId val="468335327"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="581013855"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="468335327"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="468335327"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="581013855"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1911,6 +2603,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -3460,6 +4232,1038 @@
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4049,6 +5853,42 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>64770</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>312420</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>64770</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Graphique 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{634F040F-A3B4-4E93-A316-7C3EAB938174}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4121,6 +5961,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>106680</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>34290</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>716280</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>34290</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Graphique 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67D25B60-A3D8-4CA2-B7C8-BAAAD48A149C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4737,7 +6613,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9AF43EA-3DC9-4855-BEED-2A1578264041}">
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" customWidth="1"/>
@@ -4748,14 +6624,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="A1" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -4972,8 +6848,8 @@
       <c r="F16" t="s">
         <v>5</v>
       </c>
-      <c r="H16" s="4" t="s">
-        <v>20</v>
+      <c r="H16" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -5154,234 +7030,234 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="7"/>
+      <c r="B26" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="D27" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G27" s="9"/>
-      <c r="H27" s="10" t="s">
-        <v>20</v>
+      <c r="G27" s="7"/>
+      <c r="H27" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="8">
+      <c r="A28" s="6">
         <v>0</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9">
+      <c r="B28" s="7"/>
+      <c r="C28" s="7">
         <v>0</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="7">
         <v>0</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="7">
         <v>3.21</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="7">
         <v>16470577</v>
       </c>
-      <c r="G28" s="9"/>
-      <c r="H28" s="11">
-        <f>(F28-$F$28)/$F$28</f>
+      <c r="G28" s="7"/>
+      <c r="H28" s="9">
+        <f t="shared" ref="H28:H34" si="5">(F28-$F$28)/$F$28</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="8">
+      <c r="A29" s="6">
         <v>1</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="7">
         <v>10</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="7">
         <f>1/$B29</f>
         <v>0.1</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="7">
         <f>$B$2/(2*$B29)</f>
         <v>0.01</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="7">
         <v>1.96</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="7">
         <v>26988106</v>
       </c>
-      <c r="G29" s="9"/>
-      <c r="H29" s="11">
-        <f>(F29-$F$28)/$F$28</f>
+      <c r="G29" s="7"/>
+      <c r="H29" s="9">
+        <f t="shared" si="5"/>
         <v>0.63856469630663215</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="8">
+      <c r="A30" s="6">
         <v>2</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="7">
         <v>12.5</v>
       </c>
-      <c r="C30" s="9">
-        <f t="shared" ref="C30:C34" si="5">1/$B30</f>
+      <c r="C30" s="7">
+        <f t="shared" ref="C30:C34" si="6">1/$B30</f>
         <v>0.08</v>
       </c>
-      <c r="D30" s="9">
-        <f t="shared" ref="D30:D34" si="6">$B$2/(2*$B30)</f>
+      <c r="D30" s="7">
+        <f t="shared" ref="D30:D34" si="7">$B$2/(2*$B30)</f>
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="7">
         <v>2.46</v>
       </c>
-      <c r="F30" s="9">
+      <c r="F30" s="7">
         <v>21503966</v>
       </c>
-      <c r="G30" s="9"/>
-      <c r="H30" s="11">
-        <f>(F30-$F$28)/$F$28</f>
+      <c r="G30" s="7"/>
+      <c r="H30" s="9">
+        <f t="shared" si="5"/>
         <v>0.30559882631919938</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="8">
+      <c r="A31" s="6">
         <v>3</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31" s="7">
         <v>15</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C31" s="7">
+        <f t="shared" si="6"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="D31" s="7">
+        <f t="shared" si="7"/>
+        <v>6.6666666666666671E-3</v>
+      </c>
+      <c r="E31" s="7">
+        <v>2.56</v>
+      </c>
+      <c r="F31" s="7">
+        <v>20718756</v>
+      </c>
+      <c r="G31" s="7"/>
+      <c r="H31" s="9">
         <f t="shared" si="5"/>
-        <v>6.6666666666666666E-2</v>
-      </c>
-      <c r="D31" s="9">
+        <v>0.25792532951334979</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="6">
+        <v>4</v>
+      </c>
+      <c r="B32" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="C32" s="7">
         <f t="shared" si="6"/>
-        <v>6.6666666666666671E-3</v>
-      </c>
-      <c r="E31" s="9">
-        <v>2.56</v>
-      </c>
-      <c r="F31" s="9">
-        <v>20718756</v>
-      </c>
-      <c r="G31" s="9"/>
-      <c r="H31" s="11">
-        <f>(F31-$F$28)/$F$28</f>
-        <v>0.25792532951334979</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="8">
-        <v>4</v>
-      </c>
-      <c r="B32" s="9">
-        <v>17.5</v>
-      </c>
-      <c r="C32" s="9">
+        <v>5.7142857142857141E-2</v>
+      </c>
+      <c r="D32" s="7">
+        <f t="shared" si="7"/>
+        <v>5.7142857142857143E-3</v>
+      </c>
+      <c r="E32" s="7">
+        <v>2.83</v>
+      </c>
+      <c r="F32" s="7">
+        <v>18704230</v>
+      </c>
+      <c r="G32" s="7"/>
+      <c r="H32" s="9">
         <f t="shared" si="5"/>
-        <v>5.7142857142857141E-2</v>
-      </c>
-      <c r="D32" s="9">
+        <v>0.13561473893719692</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="6">
+        <v>5</v>
+      </c>
+      <c r="B33" s="7">
+        <v>20</v>
+      </c>
+      <c r="C33" s="7">
         <f t="shared" si="6"/>
-        <v>5.7142857142857143E-3</v>
-      </c>
-      <c r="E32" s="9">
-        <v>2.83</v>
-      </c>
-      <c r="F32" s="9">
-        <v>18704230</v>
-      </c>
-      <c r="G32" s="9"/>
-      <c r="H32" s="11">
-        <f>(F32-$F$28)/$F$28</f>
-        <v>0.13561473893719692</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="8">
-        <v>5</v>
-      </c>
-      <c r="B33" s="9">
-        <v>20</v>
-      </c>
-      <c r="C33" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="D33" s="7">
+        <f t="shared" si="7"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E33" s="7">
+        <v>2.9</v>
+      </c>
+      <c r="F33" s="7">
+        <v>18229122</v>
+      </c>
+      <c r="G33" s="7"/>
+      <c r="H33" s="9">
         <f t="shared" si="5"/>
-        <v>0.05</v>
-      </c>
-      <c r="D33" s="9">
+        <v>0.10676887640305498</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="10">
+        <v>6</v>
+      </c>
+      <c r="B34" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="C34" s="11">
         <f t="shared" si="6"/>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="E33" s="9">
-        <v>2.9</v>
-      </c>
-      <c r="F33" s="9">
-        <v>18229122</v>
-      </c>
-      <c r="G33" s="9"/>
-      <c r="H33" s="11">
-        <f>(F33-$F$28)/$F$28</f>
-        <v>0.10676887640305498</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="12">
-        <v>6</v>
-      </c>
-      <c r="B34" s="13">
-        <v>22.5</v>
-      </c>
-      <c r="C34" s="13">
+        <v>4.4444444444444446E-2</v>
+      </c>
+      <c r="D34" s="11">
+        <f t="shared" si="7"/>
+        <v>4.4444444444444444E-3</v>
+      </c>
+      <c r="E34" s="11">
+        <v>2.98</v>
+      </c>
+      <c r="F34" s="11">
+        <v>17777420</v>
+      </c>
+      <c r="G34" s="11"/>
+      <c r="H34" s="12">
         <f t="shared" si="5"/>
-        <v>4.4444444444444446E-2</v>
-      </c>
-      <c r="D34" s="13">
-        <f t="shared" si="6"/>
-        <v>4.4444444444444444E-3</v>
-      </c>
-      <c r="E34" s="13">
-        <v>2.98</v>
-      </c>
-      <c r="F34" s="13">
-        <v>17777420</v>
-      </c>
-      <c r="G34" s="13"/>
-      <c r="H34" s="14">
-        <f>(F34-$F$28)/$F$28</f>
         <v>7.9344093409720859E-2</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" t="s">
         <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
@@ -5439,11 +7315,11 @@
         <v>12.5</v>
       </c>
       <c r="C41">
-        <f t="shared" ref="C41:C45" si="7">1/$B41</f>
+        <f t="shared" ref="C41:C45" si="8">1/$B41</f>
         <v>0.08</v>
       </c>
       <c r="D41">
-        <f t="shared" ref="D41:D45" si="8">$B$2/(2*$B41)</f>
+        <f t="shared" ref="D41:D45" si="9">$B$2/(2*$B41)</f>
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
@@ -5455,11 +7331,11 @@
         <v>15</v>
       </c>
       <c r="C42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="D42">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6.6666666666666671E-3</v>
       </c>
     </row>
@@ -5471,11 +7347,11 @@
         <v>17.5</v>
       </c>
       <c r="C43">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="D43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5.7142857142857143E-3</v>
       </c>
     </row>
@@ -5487,11 +7363,11 @@
         <v>20</v>
       </c>
       <c r="C44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.05</v>
       </c>
       <c r="D44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
@@ -5503,12 +7379,220 @@
         <v>22.5</v>
       </c>
       <c r="C45">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.4444444444444446E-2</v>
       </c>
       <c r="D45">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4.4444444444444444E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>22</v>
+      </c>
+      <c r="B48" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" t="s">
+        <v>5</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>0</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0.86</v>
+      </c>
+      <c r="F50">
+        <v>51130672</v>
+      </c>
+      <c r="H50">
+        <f>(F50-$F$50)/$F$50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>1</v>
+      </c>
+      <c r="B51">
+        <v>10</v>
+      </c>
+      <c r="C51">
+        <f>1/$B51</f>
+        <v>0.1</v>
+      </c>
+      <c r="D51">
+        <f>$B$2/(2*$B51)</f>
+        <v>0.01</v>
+      </c>
+      <c r="E51">
+        <v>0.79</v>
+      </c>
+      <c r="F51">
+        <v>55586384</v>
+      </c>
+      <c r="H51">
+        <f t="shared" ref="H51:H56" si="10">(F51-$F$50)/$F$50</f>
+        <v>8.7143622911899143E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>2</v>
+      </c>
+      <c r="B52">
+        <v>12.5</v>
+      </c>
+      <c r="C52">
+        <f t="shared" ref="C52:C56" si="11">1/$B52</f>
+        <v>0.08</v>
+      </c>
+      <c r="D52">
+        <f t="shared" ref="D52:D56" si="12">$B$2/(2*$B52)</f>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="E52">
+        <v>0.79</v>
+      </c>
+      <c r="F52">
+        <v>55242576</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="10"/>
+        <v>8.041951805366454E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>3</v>
+      </c>
+      <c r="B53">
+        <v>15</v>
+      </c>
+      <c r="C53">
+        <f t="shared" si="11"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="12"/>
+        <v>6.6666666666666671E-3</v>
+      </c>
+      <c r="E53">
+        <v>0.8</v>
+      </c>
+      <c r="F53">
+        <v>54902992</v>
+      </c>
+      <c r="H53">
+        <f t="shared" si="10"/>
+        <v>7.3778025057053817E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>4</v>
+      </c>
+      <c r="B54">
+        <v>17.5</v>
+      </c>
+      <c r="C54">
+        <f t="shared" si="11"/>
+        <v>5.7142857142857141E-2</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="12"/>
+        <v>5.7142857142857143E-3</v>
+      </c>
+      <c r="E54">
+        <v>0.8</v>
+      </c>
+      <c r="F54">
+        <v>54567548</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="10"/>
+        <v>6.7217501072546038E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>5</v>
+      </c>
+      <c r="B55">
+        <v>20</v>
+      </c>
+      <c r="C55">
+        <f t="shared" si="11"/>
+        <v>0.05</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="12"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E55">
+        <v>0.82</v>
+      </c>
+      <c r="F55">
+        <v>53265704</v>
+      </c>
+      <c r="H55">
+        <f t="shared" si="10"/>
+        <v>4.1756384504392979E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>6</v>
+      </c>
+      <c r="B56">
+        <v>22.5</v>
+      </c>
+      <c r="C56">
+        <f t="shared" si="11"/>
+        <v>4.4444444444444446E-2</v>
+      </c>
+      <c r="D56">
+        <f t="shared" si="12"/>
+        <v>4.4444444444444444E-3</v>
+      </c>
+      <c r="E56">
+        <v>0.84</v>
+      </c>
+      <c r="F56">
+        <v>52329284</v>
+      </c>
+      <c r="H56">
+        <f t="shared" si="10"/>
+        <v>2.3442132737860361E-2</v>
       </c>
     </row>
   </sheetData>
@@ -5524,7 +7608,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07B17566-2D0F-4854-8779-E2AD22D057CD}">
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" customWidth="1"/>
@@ -5535,14 +7619,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="A1" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -5695,7 +7779,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -5717,8 +7801,8 @@
       <c r="F16" t="s">
         <v>5</v>
       </c>
-      <c r="H16" s="4" t="s">
-        <v>20</v>
+      <c r="H16" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -5903,7 +7987,7 @@
         <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -5925,8 +8009,8 @@
       <c r="F27" t="s">
         <v>5</v>
       </c>
-      <c r="H27" s="4" t="s">
-        <v>20</v>
+      <c r="H27" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
@@ -6108,10 +8192,10 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" t="s">
         <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
@@ -6239,6 +8323,220 @@
       <c r="D45">
         <f t="shared" si="9"/>
         <v>4.2222222222222227E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>22</v>
+      </c>
+      <c r="B48" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" t="s">
+        <v>5</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>0</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>1.34</v>
+      </c>
+      <c r="F50">
+        <v>50396772</v>
+      </c>
+      <c r="H50">
+        <f>(F50-$F$50)/$F$50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>1</v>
+      </c>
+      <c r="B51">
+        <v>10</v>
+      </c>
+      <c r="C51">
+        <f>1/$B51</f>
+        <v>0.1</v>
+      </c>
+      <c r="D51">
+        <f>$B$2/(2*$B51)</f>
+        <v>9.4999999999999998E-3</v>
+      </c>
+      <c r="E51">
+        <v>1.51</v>
+      </c>
+      <c r="F51">
+        <v>44985332</v>
+      </c>
+      <c r="H51">
+        <f t="shared" ref="H51:H56" si="10">(F51-$F$50)/$F$50</f>
+        <v>-0.1073767184930019</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>2</v>
+      </c>
+      <c r="B52">
+        <v>12.5</v>
+      </c>
+      <c r="C52">
+        <f t="shared" ref="C52:C56" si="11">1/$B52</f>
+        <v>0.08</v>
+      </c>
+      <c r="D52">
+        <f t="shared" ref="D52:D56" si="12">$B$2/(2*$B52)</f>
+        <v>7.6E-3</v>
+      </c>
+      <c r="E52">
+        <v>1.45</v>
+      </c>
+      <c r="F52">
+        <v>46655528</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="10"/>
+        <v>-7.4235786371396967E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>3</v>
+      </c>
+      <c r="B53">
+        <v>15</v>
+      </c>
+      <c r="C53">
+        <f t="shared" si="11"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="12"/>
+        <v>6.3333333333333332E-3</v>
+      </c>
+      <c r="E53">
+        <v>1.44</v>
+      </c>
+      <c r="F53">
+        <v>46972584</v>
+      </c>
+      <c r="H53">
+        <f t="shared" si="10"/>
+        <v>-6.7944589784440956E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>4</v>
+      </c>
+      <c r="B54">
+        <v>17.5</v>
+      </c>
+      <c r="C54">
+        <f t="shared" si="11"/>
+        <v>5.7142857142857141E-2</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="12"/>
+        <v>5.4285714285714284E-3</v>
+      </c>
+      <c r="E54">
+        <v>1.36</v>
+      </c>
+      <c r="F54">
+        <v>49672660</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="10"/>
+        <v>-1.436822183770024E-2</v>
+      </c>
+      <c r="I54" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>5</v>
+      </c>
+      <c r="B55">
+        <v>20</v>
+      </c>
+      <c r="C55">
+        <f t="shared" si="11"/>
+        <v>0.05</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="12"/>
+        <v>4.7499999999999999E-3</v>
+      </c>
+      <c r="E55">
+        <v>1.43</v>
+      </c>
+      <c r="F55">
+        <v>47293968</v>
+      </c>
+      <c r="H55">
+        <f t="shared" si="10"/>
+        <v>-6.1567514681297446E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>6</v>
+      </c>
+      <c r="B56">
+        <v>22.5</v>
+      </c>
+      <c r="C56">
+        <f t="shared" si="11"/>
+        <v>4.4444444444444446E-2</v>
+      </c>
+      <c r="D56">
+        <f t="shared" si="12"/>
+        <v>4.2222222222222227E-3</v>
+      </c>
+      <c r="E56">
+        <v>1.3</v>
+      </c>
+      <c r="F56">
+        <v>51910084</v>
+      </c>
+      <c r="H56">
+        <f t="shared" si="10"/>
+        <v>3.0027954965052128E-2</v>
+      </c>
+      <c r="I56" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/MesureGraphiteSensor.xlsx
+++ b/MesureGraphiteSensor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\Projet_capteur\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyhai\Downloads\projet cpt\Projet_capteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD14D163-0D69-495F-ADBC-348FFBE347FF}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE272B9D-90B1-44FC-BDD2-1E77312F7FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9048" firstSheet="1" activeTab="2" xr2:uid="{26616443-A70B-4F30-8590-3C8F2284DA29}"/>
+    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" firstSheet="1" activeTab="1" xr2:uid="{26616443-A70B-4F30-8590-3C8F2284DA29}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -122,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="28">
   <si>
     <t>Graphite Sensor</t>
   </si>
@@ -200,6 +211,12 @@
   </si>
   <si>
     <t>*</t>
+  </si>
+  <si>
+    <t>Crayon 5B</t>
+  </si>
+  <si>
+    <t>Crayon 6B</t>
   </si>
 </sst>
 </file>
@@ -360,7 +377,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -372,6 +388,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1464,6 +1481,688 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
+              <c:f>'Mise en tension'!$H$61</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ΔR/R0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Mise en tension'!$D$62:$D$68</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.6666666666666671E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.7142857142857143E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.4444444444444444E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Mise en tension'!$H$62:$H$68</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2.9347244252921221</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.770687934631487</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7F1C-4D68-8D04-955A4BF50F0A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="683203103"/>
+        <c:axId val="683176703"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="683203103"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="683176703"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="683176703"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="683203103"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Mise en tension'!$H$72</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ΔR/R0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Mise en tension'!$D$73:$D$79</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.6666666666666671E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.7142857142857143E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.4444444444444444E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Mise en tension'!$H$73:$H$79</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.42367368064319594</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.40086060280999242</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.367977483260928</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.42367368064319594</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.35735638287718963</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.35735638287718963</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0C52-4BD8-9D20-BCE50BAFC95E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="683192063"/>
+        <c:axId val="683205503"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="683192063"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="683205503"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="683205503"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="683192063"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
               <c:f>'Mise en compression'!$H$16</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
@@ -1749,7 +2448,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
@@ -2103,7 +2802,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
@@ -2683,6 +3382,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -5264,6 +6043,1038 @@
 </file>
 
 <file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -5884,6 +7695,78 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>480060</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>297180</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Graphique 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5D0207E-B2D2-AD3C-8C12-B2B31577A0C3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>273423</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>26893</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>407894</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>80681</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Graphique 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63EB9DDC-A613-822F-69F5-AD48A7C6BC5F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6006,9 +7889,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6046,7 +7929,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -6152,7 +8035,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6294,7 +8177,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6613,7 +8496,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9AF43EA-3DC9-4855-BEED-2A1578264041}">
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" customWidth="1"/>
@@ -6624,14 +8507,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -7047,23 +8930,22 @@
       <c r="A27" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" t="s">
         <v>1</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" t="s">
         <v>5</v>
       </c>
-      <c r="G27" s="7"/>
-      <c r="H27" s="8" t="s">
+      <c r="H27" s="7" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7071,21 +8953,19 @@
       <c r="A28" s="6">
         <v>0</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7">
+      <c r="C28">
         <v>0</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28">
         <v>0</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28">
         <v>3.21</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28">
         <v>16470577</v>
       </c>
-      <c r="G28" s="7"/>
-      <c r="H28" s="9">
+      <c r="H28" s="8">
         <f t="shared" ref="H28:H34" si="5">(F28-$F$28)/$F$28</f>
         <v>0</v>
       </c>
@@ -7094,25 +8974,24 @@
       <c r="A29" s="6">
         <v>1</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29">
         <v>10</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29">
         <f>1/$B29</f>
         <v>0.1</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29">
         <f>$B$2/(2*$B29)</f>
         <v>0.01</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E29">
         <v>1.96</v>
       </c>
-      <c r="F29" s="7">
+      <c r="F29">
         <v>26988106</v>
       </c>
-      <c r="G29" s="7"/>
-      <c r="H29" s="9">
+      <c r="H29" s="8">
         <f t="shared" si="5"/>
         <v>0.63856469630663215</v>
       </c>
@@ -7121,25 +9000,24 @@
       <c r="A30" s="6">
         <v>2</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30">
         <v>12.5</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30">
         <f t="shared" ref="C30:C34" si="6">1/$B30</f>
         <v>0.08</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30">
         <f t="shared" ref="D30:D34" si="7">$B$2/(2*$B30)</f>
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30">
         <v>2.46</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30">
         <v>21503966</v>
       </c>
-      <c r="G30" s="7"/>
-      <c r="H30" s="9">
+      <c r="H30" s="8">
         <f t="shared" si="5"/>
         <v>0.30559882631919938</v>
       </c>
@@ -7148,25 +9026,24 @@
       <c r="A31" s="6">
         <v>3</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31">
         <v>15</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31">
         <f t="shared" si="6"/>
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31">
         <f t="shared" si="7"/>
         <v>6.6666666666666671E-3</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E31">
         <v>2.56</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31">
         <v>20718756</v>
       </c>
-      <c r="G31" s="7"/>
-      <c r="H31" s="9">
+      <c r="H31" s="8">
         <f t="shared" si="5"/>
         <v>0.25792532951334979</v>
       </c>
@@ -7175,25 +9052,24 @@
       <c r="A32" s="6">
         <v>4</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32">
         <v>17.5</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32">
         <f t="shared" si="6"/>
         <v>5.7142857142857141E-2</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32">
         <f t="shared" si="7"/>
         <v>5.7142857142857143E-3</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E32">
         <v>2.83</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32">
         <v>18704230</v>
       </c>
-      <c r="G32" s="7"/>
-      <c r="H32" s="9">
+      <c r="H32" s="8">
         <f t="shared" si="5"/>
         <v>0.13561473893719692</v>
       </c>
@@ -7202,52 +9078,51 @@
       <c r="A33" s="6">
         <v>5</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33">
         <v>20</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33">
         <f t="shared" si="6"/>
         <v>0.05</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33">
         <f t="shared" si="7"/>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E33">
         <v>2.9</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F33">
         <v>18229122</v>
       </c>
-      <c r="G33" s="7"/>
-      <c r="H33" s="9">
+      <c r="H33" s="8">
         <f t="shared" si="5"/>
         <v>0.10676887640305498</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="10">
+      <c r="A34" s="9">
         <v>6</v>
       </c>
-      <c r="B34" s="11">
+      <c r="B34" s="10">
         <v>22.5</v>
       </c>
-      <c r="C34" s="11">
+      <c r="C34" s="10">
         <f t="shared" si="6"/>
         <v>4.4444444444444446E-2</v>
       </c>
-      <c r="D34" s="11">
+      <c r="D34" s="10">
         <f t="shared" si="7"/>
         <v>4.4444444444444444E-3</v>
       </c>
-      <c r="E34" s="11">
+      <c r="E34" s="10">
         <v>2.98</v>
       </c>
-      <c r="F34" s="11">
+      <c r="F34" s="10">
         <v>17777420</v>
       </c>
-      <c r="G34" s="11"/>
-      <c r="H34" s="12">
+      <c r="G34" s="10"/>
+      <c r="H34" s="11">
         <f t="shared" si="5"/>
         <v>7.9344093409720859E-2</v>
       </c>
@@ -7414,7 +9289,7 @@
       <c r="F49" t="s">
         <v>5</v>
       </c>
-      <c r="H49" s="8" t="s">
+      <c r="H49" s="7" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7593,6 +9468,422 @@
       <c r="H56">
         <f t="shared" si="10"/>
         <v>2.3442132737860361E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>26</v>
+      </c>
+      <c r="B60" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>6</v>
+      </c>
+      <c r="B61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" t="s">
+        <v>10</v>
+      </c>
+      <c r="D61" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" t="s">
+        <v>1</v>
+      </c>
+      <c r="F61" t="s">
+        <v>5</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>0</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>0.34</v>
+      </c>
+      <c r="F62">
+        <v>201185104</v>
+      </c>
+      <c r="H62">
+        <f>(F62-$F$50)/$F$50</f>
+        <v>2.9347244252921221</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>1</v>
+      </c>
+      <c r="B63">
+        <v>10</v>
+      </c>
+      <c r="C63">
+        <f>1/$B63</f>
+        <v>0.1</v>
+      </c>
+      <c r="D63">
+        <f>$B$2/(2*$B63)</f>
+        <v>0.01</v>
+      </c>
+      <c r="E63">
+        <v>0.79</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <f t="shared" ref="H63:H68" si="13">(F63-$F$50)/$F$50</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>2</v>
+      </c>
+      <c r="B64">
+        <v>12.5</v>
+      </c>
+      <c r="C64">
+        <f t="shared" ref="C64:C68" si="14">1/$B64</f>
+        <v>0.08</v>
+      </c>
+      <c r="D64">
+        <f t="shared" ref="D64:D68" si="15">$B$2/(2*$B64)</f>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="E64">
+        <v>0.79</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <f t="shared" si="13"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>3</v>
+      </c>
+      <c r="B65">
+        <v>15</v>
+      </c>
+      <c r="C65">
+        <f t="shared" si="14"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="D65">
+        <f t="shared" si="15"/>
+        <v>6.6666666666666671E-3</v>
+      </c>
+      <c r="E65">
+        <v>0.8</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <f t="shared" si="13"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>4</v>
+      </c>
+      <c r="B66">
+        <v>17.5</v>
+      </c>
+      <c r="C66">
+        <f t="shared" si="14"/>
+        <v>5.7142857142857141E-2</v>
+      </c>
+      <c r="D66">
+        <f t="shared" si="15"/>
+        <v>5.7142857142857143E-3</v>
+      </c>
+      <c r="E66">
+        <v>0.8</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <f t="shared" si="13"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>5</v>
+      </c>
+      <c r="B67">
+        <v>20</v>
+      </c>
+      <c r="C67">
+        <f t="shared" si="14"/>
+        <v>0.05</v>
+      </c>
+      <c r="D67">
+        <f t="shared" si="15"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E67">
+        <v>0.82</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <f t="shared" si="13"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>6</v>
+      </c>
+      <c r="B68">
+        <v>22.5</v>
+      </c>
+      <c r="C68">
+        <f t="shared" si="14"/>
+        <v>4.4444444444444446E-2</v>
+      </c>
+      <c r="D68">
+        <f t="shared" si="15"/>
+        <v>4.4444444444444444E-3</v>
+      </c>
+      <c r="E68">
+        <v>0.35</v>
+      </c>
+      <c r="F68">
+        <v>192797808</v>
+      </c>
+      <c r="H68">
+        <f t="shared" si="13"/>
+        <v>2.770687934631487</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B71" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>6</v>
+      </c>
+      <c r="B72" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" t="s">
+        <v>10</v>
+      </c>
+      <c r="D72" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" t="s">
+        <v>1</v>
+      </c>
+      <c r="F72" t="s">
+        <v>5</v>
+      </c>
+      <c r="H72" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>0</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>0.95</v>
+      </c>
+      <c r="F73">
+        <v>46112256</v>
+      </c>
+      <c r="H73">
+        <f>(F73-$F$73)/$F$73</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>1</v>
+      </c>
+      <c r="B74">
+        <v>10</v>
+      </c>
+      <c r="C74">
+        <f>1/$B74</f>
+        <v>0.1</v>
+      </c>
+      <c r="D74">
+        <f>$B$2/(2*$B74)</f>
+        <v>0.01</v>
+      </c>
+      <c r="E74">
+        <v>0.6</v>
+      </c>
+      <c r="F74">
+        <v>72793392</v>
+      </c>
+      <c r="H74">
+        <f t="shared" ref="H74:H79" si="16">(F74-$F$50)/$F$50</f>
+        <v>0.42367368064319594</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>2</v>
+      </c>
+      <c r="B75">
+        <v>12.5</v>
+      </c>
+      <c r="C75">
+        <f t="shared" ref="C75:C79" si="17">1/$B75</f>
+        <v>0.08</v>
+      </c>
+      <c r="D75">
+        <f t="shared" ref="D75:D79" si="18">$B$2/(2*$B75)</f>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="E75">
+        <v>0.61</v>
+      </c>
+      <c r="F75">
+        <v>71626944</v>
+      </c>
+      <c r="H75">
+        <f t="shared" si="16"/>
+        <v>0.40086060280999242</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>3</v>
+      </c>
+      <c r="B76">
+        <v>15</v>
+      </c>
+      <c r="C76">
+        <f t="shared" si="17"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="D76">
+        <f t="shared" si="18"/>
+        <v>6.6666666666666671E-3</v>
+      </c>
+      <c r="E76">
+        <v>0.6</v>
+      </c>
+      <c r="F76">
+        <v>69945608</v>
+      </c>
+      <c r="H76">
+        <f t="shared" si="16"/>
+        <v>0.367977483260928</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>4</v>
+      </c>
+      <c r="B77">
+        <v>17.5</v>
+      </c>
+      <c r="C77">
+        <f t="shared" si="17"/>
+        <v>5.7142857142857141E-2</v>
+      </c>
+      <c r="D77">
+        <f t="shared" si="18"/>
+        <v>5.7142857142857143E-3</v>
+      </c>
+      <c r="E77">
+        <v>0.61</v>
+      </c>
+      <c r="F77">
+        <v>72793392</v>
+      </c>
+      <c r="H77">
+        <f t="shared" si="16"/>
+        <v>0.42367368064319594</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>5</v>
+      </c>
+      <c r="B78">
+        <v>20</v>
+      </c>
+      <c r="C78">
+        <f t="shared" si="17"/>
+        <v>0.05</v>
+      </c>
+      <c r="D78">
+        <f t="shared" si="18"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E78">
+        <v>0.64</v>
+      </c>
+      <c r="F78">
+        <v>69402544</v>
+      </c>
+      <c r="H78">
+        <f t="shared" si="16"/>
+        <v>0.35735638287718963</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>6</v>
+      </c>
+      <c r="B79">
+        <v>22.5</v>
+      </c>
+      <c r="C79">
+        <f t="shared" si="17"/>
+        <v>4.4444444444444446E-2</v>
+      </c>
+      <c r="D79">
+        <f t="shared" si="18"/>
+        <v>4.4444444444444444E-3</v>
+      </c>
+      <c r="E79">
+        <v>0.62</v>
+      </c>
+      <c r="F79">
+        <v>69402544</v>
+      </c>
+      <c r="H79">
+        <f t="shared" si="16"/>
+        <v>0.35735638287718963</v>
       </c>
     </row>
   </sheetData>
@@ -7608,7 +9899,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07B17566-2D0F-4854-8779-E2AD22D057CD}">
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" customWidth="1"/>
@@ -7619,14 +9910,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -8538,6 +10829,9 @@
       <c r="I56" t="s">
         <v>25</v>
       </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H61" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/MesureGraphiteSensor.xlsx
+++ b/MesureGraphiteSensor.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyhai\Downloads\projet cpt\Projet_capteur\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\Projet\Projet_capteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE272B9D-90B1-44FC-BDD2-1E77312F7FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B4EA0D1-F1FF-44B9-91FA-DC71FE0C9E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" firstSheet="1" activeTab="1" xr2:uid="{26616443-A70B-4F30-8590-3C8F2284DA29}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{26616443-A70B-4F30-8590-3C8F2284DA29}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="31">
   <si>
     <t>Graphite Sensor</t>
   </si>
@@ -217,6 +217,15 @@
   </si>
   <si>
     <t>Crayon 6B</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>dR/R</t>
+  </si>
+  <si>
+    <t>2HB</t>
   </si>
 </sst>
 </file>
@@ -382,13 +391,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -409,7 +418,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -749,7 +758,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1089,7 +1098,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1429,7 +1438,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1771,7 +1780,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1821,20 +1830,11 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Mise en tension'!$H$72</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ΔR/R0</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -1856,29 +1856,26 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Mise en tension'!$D$73:$D$79</c:f>
+              <c:f>'Mise en tension'!$S$7:$S$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.01</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.01</c:v>
+                  <c:v>8.0000000000000002E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.0000000000000002E-3</c:v>
+                  <c:v>6.6666666666666671E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.6666666666666671E-3</c:v>
+                  <c:v>5.7142857142857143E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.7142857142857143E-3</c:v>
+                  <c:v>5.0000000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.0000000000000001E-3</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>4.4444444444444444E-3</c:v>
                 </c:pt>
               </c:numCache>
@@ -1886,30 +1883,27 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Mise en tension'!$H$73:$H$79</c:f>
+              <c:f>'Mise en tension'!$U$7:$U$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.98002547921252203</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.42367368064319594</c:v>
+                  <c:v>1.1286303960038182</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.40086060280999242</c:v>
+                  <c:v>1.1601525119423204</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.367977483260928</c:v>
+                  <c:v>1.5419142828024899</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.42367368064319594</c:v>
+                  <c:v>1.5106700565751112</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.35735638287718963</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.35735638287718963</c:v>
+                  <c:v>1.5610367681825863</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1917,7 +1911,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0C52-4BD8-9D20-BCE50BAFC95E}"/>
+              <c16:uniqueId val="{00000000-685B-424E-8769-7EE44BAA21FB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1929,11 +1923,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="683192063"/>
-        <c:axId val="683205503"/>
+        <c:axId val="797532224"/>
+        <c:axId val="716433920"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="683192063"/>
+        <c:axId val="797532224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1990,12 +1984,12 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="683205503"/>
+        <c:crossAx val="716433920"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="683205503"/>
+        <c:axId val="716433920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2052,7 +2046,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="683192063"/>
+        <c:crossAx val="797532224"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2111,7 +2105,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2451,7 +2445,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2805,7 +2799,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7702,16 +7696,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>480060</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>263338</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>176604</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>297180</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>82363</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>176605</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7738,23 +7732,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>273423</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>26893</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>196102</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>178509</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>407894</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>80681</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>786204</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>51098</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="8" name="Graphique 7">
+        <xdr:cNvPr id="10" name="Chart 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63EB9DDC-A613-822F-69F5-AD48A7C6BC5F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF399DFA-BB29-37E6-B586-CF98E426C996}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7889,7 +7883,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -8186,7 +8180,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82D11D32-753C-406C-A8AF-6D384DFD9D4A}">
   <dimension ref="A1:E27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.44140625" customWidth="1"/>
     <col min="3" max="3" width="19.5546875" customWidth="1"/>
@@ -8496,27 +8490,28 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9AF43EA-3DC9-4855-BEED-2A1578264041}">
-  <dimension ref="A1:H79"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U79"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" customWidth="1"/>
     <col min="2" max="2" width="7.77734375" customWidth="1"/>
     <col min="3" max="3" width="15.33203125" customWidth="1"/>
     <col min="4" max="4" width="18.109375" customWidth="1"/>
     <col min="6" max="6" width="18.6640625" customWidth="1"/>
+    <col min="19" max="19" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -8527,15 +8522,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="T4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -8554,8 +8552,17 @@
       <c r="F5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="S5" t="s">
+        <v>28</v>
+      </c>
+      <c r="T5" t="s">
+        <v>29</v>
+      </c>
+      <c r="U5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0</v>
       </c>
@@ -8571,8 +8578,18 @@
       <c r="F6">
         <v>80146904</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>80146904</v>
+      </c>
+      <c r="U6">
+        <f>(T6-$T$6)/($T$6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -8593,8 +8610,19 @@
       <c r="F7">
         <v>158692912</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="S7">
+        <f>$B$2/(2*$B7)</f>
+        <v>0.01</v>
+      </c>
+      <c r="T7">
+        <v>158692912</v>
+      </c>
+      <c r="U7">
+        <f t="shared" ref="U7:U12" si="0">(T7-$T$6)/($T$6)</f>
+        <v>0.98002547921252203</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2</v>
       </c>
@@ -8602,11 +8630,11 @@
         <v>12.5</v>
       </c>
       <c r="C8">
-        <f t="shared" ref="C8:C12" si="0">1/$B8</f>
+        <f t="shared" ref="C8:C12" si="1">1/$B8</f>
         <v>0.08</v>
       </c>
       <c r="D8">
-        <f t="shared" ref="D8:D12" si="1">$B$2/(2*$B8)</f>
+        <f t="shared" ref="D8:D12" si="2">$B$2/(2*$B8)</f>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="E8">
@@ -8615,8 +8643,19 @@
       <c r="F8">
         <v>170603136</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="S8">
+        <f t="shared" ref="S8:S12" si="3">$B$2/(2*$B8)</f>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="T8">
+        <v>170603136</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="0"/>
+        <v>1.1286303960038182</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>3</v>
       </c>
@@ -8624,11 +8663,11 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="D9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.6666666666666671E-3</v>
       </c>
       <c r="E9">
@@ -8637,8 +8676,19 @@
       <c r="F9">
         <v>173129536</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="S9">
+        <f t="shared" si="3"/>
+        <v>6.6666666666666671E-3</v>
+      </c>
+      <c r="T9">
+        <v>173129536</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="0"/>
+        <v>1.1601525119423204</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>4</v>
       </c>
@@ -8646,11 +8696,11 @@
         <v>17.5</v>
       </c>
       <c r="C10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="D10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.7142857142857143E-3</v>
       </c>
       <c r="E10">
@@ -8659,8 +8709,19 @@
       <c r="F10">
         <v>203726560</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="S10">
+        <f t="shared" si="3"/>
+        <v>5.7142857142857143E-3</v>
+      </c>
+      <c r="T10">
+        <v>203726560</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="0"/>
+        <v>1.5419142828024899</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>5</v>
       </c>
@@ -8668,11 +8729,11 @@
         <v>20</v>
       </c>
       <c r="C11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.05</v>
       </c>
       <c r="D11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="E11">
@@ -8681,8 +8742,19 @@
       <c r="F11">
         <v>201222432</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="S11">
+        <f t="shared" si="3"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="T11">
+        <v>201222432</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="0"/>
+        <v>1.5106700565751112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>6</v>
       </c>
@@ -8690,11 +8762,11 @@
         <v>22.5</v>
       </c>
       <c r="C12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.4444444444444446E-2</v>
       </c>
       <c r="D12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.4444444444444444E-3</v>
       </c>
       <c r="E12">
@@ -8703,8 +8775,19 @@
       <c r="F12">
         <v>205259168</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="S12">
+        <f t="shared" si="3"/>
+        <v>4.4444444444444444E-3</v>
+      </c>
+      <c r="T12">
+        <v>205259168</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="0"/>
+        <v>1.5610367681825863</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -8712,7 +8795,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -8778,7 +8861,7 @@
         <v>42612940</v>
       </c>
       <c r="H18">
-        <f t="shared" ref="H18:H23" si="2">(F18-$F$17)/$F$17</f>
+        <f t="shared" ref="H18:H23" si="4">(F18-$F$17)/$F$17</f>
         <v>9.2292530259875397E-2</v>
       </c>
     </row>
@@ -8790,11 +8873,11 @@
         <v>12.5</v>
       </c>
       <c r="C19">
-        <f t="shared" ref="C19:C23" si="3">1/$B19</f>
+        <f t="shared" ref="C19:C23" si="5">1/$B19</f>
         <v>0.08</v>
       </c>
       <c r="D19">
-        <f t="shared" ref="D19:D23" si="4">$B$2/(2*$B19)</f>
+        <f t="shared" ref="D19:D23" si="6">$B$2/(2*$B19)</f>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="E19">
@@ -8804,7 +8887,7 @@
         <v>49733432</v>
       </c>
       <c r="H19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.27481127276802436</v>
       </c>
     </row>
@@ -8816,11 +8899,11 @@
         <v>15</v>
       </c>
       <c r="C20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="D20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6.6666666666666671E-3</v>
       </c>
       <c r="E20">
@@ -8830,7 +8913,7 @@
         <v>51813704</v>
       </c>
       <c r="H20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.32813464277039384</v>
       </c>
     </row>
@@ -8842,11 +8925,11 @@
         <v>17.5</v>
       </c>
       <c r="C21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="D21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>5.7142857142857143E-3</v>
       </c>
       <c r="E21">
@@ -8856,7 +8939,7 @@
         <v>57380384</v>
       </c>
       <c r="H21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.47082470316864478</v>
       </c>
     </row>
@@ -8868,11 +8951,11 @@
         <v>20</v>
       </c>
       <c r="C22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.05</v>
       </c>
       <c r="D22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="E22">
@@ -8882,7 +8965,7 @@
         <v>60636680</v>
       </c>
       <c r="H22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.55429295945687818</v>
       </c>
     </row>
@@ -8894,11 +8977,11 @@
         <v>22.5</v>
       </c>
       <c r="C23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4.4444444444444446E-2</v>
       </c>
       <c r="D23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>4.4444444444444444E-3</v>
       </c>
       <c r="E23">
@@ -8908,7 +8991,7 @@
         <v>60400312</v>
       </c>
       <c r="H23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.54823416602951858</v>
       </c>
     </row>
@@ -8966,7 +9049,7 @@
         <v>16470577</v>
       </c>
       <c r="H28" s="8">
-        <f t="shared" ref="H28:H34" si="5">(F28-$F$28)/$F$28</f>
+        <f t="shared" ref="H28:H34" si="7">(F28-$F$28)/$F$28</f>
         <v>0</v>
       </c>
     </row>
@@ -8992,7 +9075,7 @@
         <v>26988106</v>
       </c>
       <c r="H29" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.63856469630663215</v>
       </c>
     </row>
@@ -9004,11 +9087,11 @@
         <v>12.5</v>
       </c>
       <c r="C30">
-        <f t="shared" ref="C30:C34" si="6">1/$B30</f>
+        <f t="shared" ref="C30:C34" si="8">1/$B30</f>
         <v>0.08</v>
       </c>
       <c r="D30">
-        <f t="shared" ref="D30:D34" si="7">$B$2/(2*$B30)</f>
+        <f t="shared" ref="D30:D34" si="9">$B$2/(2*$B30)</f>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="E30">
@@ -9018,7 +9101,7 @@
         <v>21503966</v>
       </c>
       <c r="H30" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.30559882631919938</v>
       </c>
     </row>
@@ -9030,11 +9113,11 @@
         <v>15</v>
       </c>
       <c r="C31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="D31">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>6.6666666666666671E-3</v>
       </c>
       <c r="E31">
@@ -9044,7 +9127,7 @@
         <v>20718756</v>
       </c>
       <c r="H31" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.25792532951334979</v>
       </c>
     </row>
@@ -9056,11 +9139,11 @@
         <v>17.5</v>
       </c>
       <c r="C32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="D32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>5.7142857142857143E-3</v>
       </c>
       <c r="E32">
@@ -9070,7 +9153,7 @@
         <v>18704230</v>
       </c>
       <c r="H32" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.13561473893719692</v>
       </c>
     </row>
@@ -9082,11 +9165,11 @@
         <v>20</v>
       </c>
       <c r="C33">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.05</v>
       </c>
       <c r="D33">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="E33">
@@ -9096,7 +9179,7 @@
         <v>18229122</v>
       </c>
       <c r="H33" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.10676887640305498</v>
       </c>
     </row>
@@ -9108,11 +9191,11 @@
         <v>22.5</v>
       </c>
       <c r="C34" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>4.4444444444444446E-2</v>
       </c>
       <c r="D34" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>4.4444444444444444E-3</v>
       </c>
       <c r="E34" s="10">
@@ -9123,7 +9206,7 @@
       </c>
       <c r="G34" s="10"/>
       <c r="H34" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>7.9344093409720859E-2</v>
       </c>
     </row>
@@ -9190,11 +9273,11 @@
         <v>12.5</v>
       </c>
       <c r="C41">
-        <f t="shared" ref="C41:C45" si="8">1/$B41</f>
+        <f t="shared" ref="C41:C45" si="10">1/$B41</f>
         <v>0.08</v>
       </c>
       <c r="D41">
-        <f t="shared" ref="D41:D45" si="9">$B$2/(2*$B41)</f>
+        <f t="shared" ref="D41:D45" si="11">$B$2/(2*$B41)</f>
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
@@ -9206,11 +9289,11 @@
         <v>15</v>
       </c>
       <c r="C42">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="D42">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>6.6666666666666671E-3</v>
       </c>
     </row>
@@ -9222,11 +9305,11 @@
         <v>17.5</v>
       </c>
       <c r="C43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="D43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>5.7142857142857143E-3</v>
       </c>
     </row>
@@ -9238,11 +9321,11 @@
         <v>20</v>
       </c>
       <c r="C44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.05</v>
       </c>
       <c r="D44">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
@@ -9254,11 +9337,11 @@
         <v>22.5</v>
       </c>
       <c r="C45">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>4.4444444444444446E-2</v>
       </c>
       <c r="D45">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>4.4444444444444444E-3</v>
       </c>
     </row>
@@ -9336,7 +9419,7 @@
         <v>55586384</v>
       </c>
       <c r="H51">
-        <f t="shared" ref="H51:H56" si="10">(F51-$F$50)/$F$50</f>
+        <f t="shared" ref="H51:H56" si="12">(F51-$F$50)/$F$50</f>
         <v>8.7143622911899143E-2</v>
       </c>
     </row>
@@ -9348,11 +9431,11 @@
         <v>12.5</v>
       </c>
       <c r="C52">
-        <f t="shared" ref="C52:C56" si="11">1/$B52</f>
+        <f t="shared" ref="C52:C56" si="13">1/$B52</f>
         <v>0.08</v>
       </c>
       <c r="D52">
-        <f t="shared" ref="D52:D56" si="12">$B$2/(2*$B52)</f>
+        <f t="shared" ref="D52:D56" si="14">$B$2/(2*$B52)</f>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="E52">
@@ -9362,7 +9445,7 @@
         <v>55242576</v>
       </c>
       <c r="H52">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>8.041951805366454E-2</v>
       </c>
     </row>
@@ -9374,11 +9457,11 @@
         <v>15</v>
       </c>
       <c r="C53">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="D53">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>6.6666666666666671E-3</v>
       </c>
       <c r="E53">
@@ -9388,7 +9471,7 @@
         <v>54902992</v>
       </c>
       <c r="H53">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>7.3778025057053817E-2</v>
       </c>
     </row>
@@ -9400,11 +9483,11 @@
         <v>17.5</v>
       </c>
       <c r="C54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="D54">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>5.7142857142857143E-3</v>
       </c>
       <c r="E54">
@@ -9414,7 +9497,7 @@
         <v>54567548</v>
       </c>
       <c r="H54">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>6.7217501072546038E-2</v>
       </c>
     </row>
@@ -9426,11 +9509,11 @@
         <v>20</v>
       </c>
       <c r="C55">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.05</v>
       </c>
       <c r="D55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="E55">
@@ -9440,7 +9523,7 @@
         <v>53265704</v>
       </c>
       <c r="H55">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>4.1756384504392979E-2</v>
       </c>
     </row>
@@ -9452,11 +9535,11 @@
         <v>22.5</v>
       </c>
       <c r="C56">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>4.4444444444444446E-2</v>
       </c>
       <c r="D56">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>4.4444444444444444E-3</v>
       </c>
       <c r="E56">
@@ -9466,7 +9549,7 @@
         <v>52329284</v>
       </c>
       <c r="H56">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>2.3442132737860361E-2</v>
       </c>
     </row>
@@ -9544,7 +9627,7 @@
         <v>0</v>
       </c>
       <c r="H63">
-        <f t="shared" ref="H63:H68" si="13">(F63-$F$50)/$F$50</f>
+        <f t="shared" ref="H63:H68" si="15">(F63-$F$50)/$F$50</f>
         <v>-1</v>
       </c>
     </row>
@@ -9556,11 +9639,11 @@
         <v>12.5</v>
       </c>
       <c r="C64">
-        <f t="shared" ref="C64:C68" si="14">1/$B64</f>
+        <f t="shared" ref="C64:C68" si="16">1/$B64</f>
         <v>0.08</v>
       </c>
       <c r="D64">
-        <f t="shared" ref="D64:D68" si="15">$B$2/(2*$B64)</f>
+        <f t="shared" ref="D64:D68" si="17">$B$2/(2*$B64)</f>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="E64">
@@ -9570,7 +9653,7 @@
         <v>0</v>
       </c>
       <c r="H64">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-1</v>
       </c>
     </row>
@@ -9582,11 +9665,11 @@
         <v>15</v>
       </c>
       <c r="C65">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="D65">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>6.6666666666666671E-3</v>
       </c>
       <c r="E65">
@@ -9596,7 +9679,7 @@
         <v>0</v>
       </c>
       <c r="H65">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-1</v>
       </c>
     </row>
@@ -9608,11 +9691,11 @@
         <v>17.5</v>
       </c>
       <c r="C66">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="D66">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>5.7142857142857143E-3</v>
       </c>
       <c r="E66">
@@ -9622,7 +9705,7 @@
         <v>0</v>
       </c>
       <c r="H66">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-1</v>
       </c>
     </row>
@@ -9634,11 +9717,11 @@
         <v>20</v>
       </c>
       <c r="C67">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.05</v>
       </c>
       <c r="D67">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="E67">
@@ -9648,7 +9731,7 @@
         <v>0</v>
       </c>
       <c r="H67">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-1</v>
       </c>
     </row>
@@ -9660,11 +9743,11 @@
         <v>22.5</v>
       </c>
       <c r="C68">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>4.4444444444444446E-2</v>
       </c>
       <c r="D68">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>4.4444444444444444E-3</v>
       </c>
       <c r="E68">
@@ -9674,12 +9757,12 @@
         <v>192797808</v>
       </c>
       <c r="H68">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>2.770687934631487</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="14" t="s">
+      <c r="A71" s="12" t="s">
         <v>27</v>
       </c>
       <c r="B71" t="s">
@@ -9752,7 +9835,7 @@
         <v>72793392</v>
       </c>
       <c r="H74">
-        <f t="shared" ref="H74:H79" si="16">(F74-$F$50)/$F$50</f>
+        <f t="shared" ref="H74:H79" si="18">(F74-$F$50)/$F$50</f>
         <v>0.42367368064319594</v>
       </c>
     </row>
@@ -9764,11 +9847,11 @@
         <v>12.5</v>
       </c>
       <c r="C75">
-        <f t="shared" ref="C75:C79" si="17">1/$B75</f>
+        <f t="shared" ref="C75:C79" si="19">1/$B75</f>
         <v>0.08</v>
       </c>
       <c r="D75">
-        <f t="shared" ref="D75:D79" si="18">$B$2/(2*$B75)</f>
+        <f t="shared" ref="D75:D79" si="20">$B$2/(2*$B75)</f>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="E75">
@@ -9778,7 +9861,7 @@
         <v>71626944</v>
       </c>
       <c r="H75">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.40086060280999242</v>
       </c>
     </row>
@@ -9790,11 +9873,11 @@
         <v>15</v>
       </c>
       <c r="C76">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="D76">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>6.6666666666666671E-3</v>
       </c>
       <c r="E76">
@@ -9804,7 +9887,7 @@
         <v>69945608</v>
       </c>
       <c r="H76">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.367977483260928</v>
       </c>
     </row>
@@ -9816,11 +9899,11 @@
         <v>17.5</v>
       </c>
       <c r="C77">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="D77">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>5.7142857142857143E-3</v>
       </c>
       <c r="E77">
@@ -9830,7 +9913,7 @@
         <v>72793392</v>
       </c>
       <c r="H77">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.42367368064319594</v>
       </c>
     </row>
@@ -9842,11 +9925,11 @@
         <v>20</v>
       </c>
       <c r="C78">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.05</v>
       </c>
       <c r="D78">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="E78">
@@ -9856,7 +9939,7 @@
         <v>69402544</v>
       </c>
       <c r="H78">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.35735638287718963</v>
       </c>
     </row>
@@ -9868,11 +9951,11 @@
         <v>22.5</v>
       </c>
       <c r="C79">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>4.4444444444444446E-2</v>
       </c>
       <c r="D79">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>4.4444444444444444E-3</v>
       </c>
       <c r="E79">
@@ -9882,7 +9965,7 @@
         <v>69402544</v>
       </c>
       <c r="H79">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.35735638287718963</v>
       </c>
     </row>
@@ -9900,7 +9983,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07B17566-2D0F-4854-8779-E2AD22D057CD}">
   <dimension ref="A1:I61"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" customWidth="1"/>
     <col min="2" max="2" width="13.88671875" customWidth="1"/>
@@ -9910,14 +9993,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
